--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d419b71a5a3ad5ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
+          <t>https://www.indeed.com/viewjob?jk=35e6a0def13e14e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Analytics Engineer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
+          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BONbLOC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Applied Architect (.NET &amp; Databricks)</t>
+          <t>Data Scientist / Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
+          <t>https://www.indeed.com/viewjob?jk=778c7417749e5f6c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd53c43d1a2a4e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>BONbLOC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
+          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>AI Applied Architect (.NET &amp; Databricks)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hempstead, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tergar International</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
+          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
+          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Hempstead, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
+          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Automation Architect – AI, Cloud &amp; Quality Engineering</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8019de144986634a</t>
+          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>DevIQ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Hadoop, HDFS, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da84632d9568dfce</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f856ad60bd043712</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=53d88228d05e3236</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Teachers Retirement System</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr SW Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af90d11c5660ec74</t>
+          <t>https://www.indeed.com/viewjob?jk=3945a7642806e1c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=de9d58d7eace2bbb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,28 +1497,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=80a7c0cf27c653aa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b24821c22dce160</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DATA Engineer with Healthcare background</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior AWS Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Teachers Retirement System</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Database</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97fb5b4fe767905</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2fcea5b61df0eb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HDI Global Insurance Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094f4152c1c3b844</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a5812a0d08b16b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Platform Architect</t>
+          <t>Sr SW Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Synergy BIS</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, PostgreSQL, MySQL, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd743c87589a9510</t>
+          <t>https://www.indeed.com/viewjob?jk=af90d11c5660ec74</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Fintech)</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2939e578451e049f</t>
+          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack Developer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Benda Infotech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, PostgreSQL, NoSQL, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c284602b40afa505</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI ML Data Scientist</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, YARN, Spark, PySpark, Kafka, Oracle, NoSQL, Tableau, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce609bae5ee0d5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior DATA Engineer with Healthcare background</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=f743bc33db99ea9d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
+          <t>https://www.indeed.com/viewjob?jk=7dda9069c1d0d6e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior AWS Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>HDI Global Insurance Company</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=094f4152c1c3b844</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevX / Developer Operations (Partner 16, Partner 18), ASG</t>
+          <t>Java Full Stack Engineer (Fintech)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2570942407162c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2939e578451e049f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
@@ -2573,20 +2573,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec276bec6c38a67</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Resident Solutions Architect - Digital Native Business</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377873b4a91a42db</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Engineer - AI Forward Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CarParts.com</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Data Modeling, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7e89cef9a97da</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3dcc861e4ac768</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,54 +2876,54 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a7e8374973c1f3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote - United States)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea9c4a4c56af0d7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Application Engineer IV</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,89 +3051,89 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96178a2a524d96e</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Model Risk Management</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Vertex AI, Snowflake, ETL, MLflow, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4b8c7a56e0e088</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Programmer</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,77 +3366,1792 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f708bb2089c8e37e</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SAS Developer (with Admin Background)</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Manufacturing Data Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ion Storage Systems</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Beltsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Engineer (Remote - United States)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02fe9ec908f659c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>OpenShift Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59f16b492e7cc754</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Managed Services Engineer III</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CoorsTek</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Application Engineer IV</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fort Meade, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Engineer III, Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Omnicell</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Cranberry Township, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>In-N-Out Burger</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer III (Platform)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MAPFRE Insurance</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Webster, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VetsEZ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Nexxen</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a96178a2a524d96e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>endava</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sr. Programmer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Salesforce Technical Architect, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NeuraFlash, Part of Accenture</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D118" t="n">
         <v>10.4</v>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b030dd9a627fd2c</t>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3df4cadd2708adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e331a82a4ab0113</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fa148b4d76cb12</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0941e3a211072d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82e649d860885dd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e8e06e7d196990</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=408d36db3edc62d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55d828aded70aa48</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57fb0b293b6e45b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7d3f157d5d4e121</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eb49350fc0c3bff</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c2051a8e908817c</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff83660440c0810b</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5263c067a9d93c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0254aaa4115a0f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d6ce4a2306c3a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4128a682c7bf9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5b0a184e6ed2c87</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d419b71a5a3ad5ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e6a0def13e14e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Data Scientist / Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BONbLOC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
+          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Analytics Engineer</t>
+          <t>AI Applied Architect (.NET &amp; Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tergar International</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=778c7417749e5f6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Decision Foundry</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd53c43d1a2a4e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BONbLOC</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Applied Architect (.NET &amp; Databricks)</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tergar International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Hempstead, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
+          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
+          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>DevIQ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hempstead, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
+          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior ETL Developer (Azure &amp; MDM/Reltio Focus)</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde84b2e0c4d7b5</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f856ad60bd043712</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Full Stack Developer</t>
+          <t>Senior AWS Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Teachers Retirement System</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d88228d05e3236</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3945a7642806e1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure (OCI) Engineer</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9d58d7eace2bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,46 +1497,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80a7c0cf27c653aa</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b24821c22dce160</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Senior DATA Engineer with Healthcare background</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teachers Retirement System</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2fcea5b61df0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior AWS Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a5812a0d08b16b</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr SW Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>HDI Global Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,269 +1791,269 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af90d11c5660ec74</t>
+          <t>https://www.indeed.com/viewjob?jk=094f4152c1c3b844</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf613962496b27</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DATA Engineer with Healthcare background</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f743bc33db99ea9d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dda9069c1d0d6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AWS Data Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HDI Global Insurance Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094f4152c1c3b844</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Fintech)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2939e578451e049f</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,392 +2516,392 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,417 +2911,417 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a7e8374973c1f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea9c4a4c56af0d7</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,242 +3331,242 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote - United States)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02fe9ec908f659c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OpenShift Engineer</t>
+          <t>Java Full Stack Engineer (Fintech)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CADRE GOVERNMENT SOLUTIONS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f16b492e7cc754</t>
+          <t>https://www.indeed.com/viewjob?jk=2939e578451e049f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Application Engineer IV</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,137 +3751,137 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a96178a2a524d96e</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Programmer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Salesforce Technical Architect, Data &amp; AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NeuraFlash, Part of Accenture</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3420dddc661e222d</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,102 +4451,102 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3df4cadd2708adf</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e331a82a4ab0113</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fa148b4d76cb12</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0941e3a211072d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Engineer (Remote - United States)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e649d860885dd8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,14 +4731,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8e06e7d196990</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408d36db3edc62d2</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d828aded70aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Application Engineer IV</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fb0b293b6e45b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Engineer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Omnicell</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d3f157d5d4e121</t>
+          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb49350fc0c3bff</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2051a8e908817c</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff83660440c0810b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5263c067a9d93c2</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0254aaa4115a0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6ce4a2306c3a92</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4128a682c7bf9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,15 +5141,1065 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3df4cadd2708adf</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e331a82a4ab0113</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0fa148b4d76cb12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0941e3a211072d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82e649d860885dd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e8e06e7d196990</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=408d36db3edc62d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55d828aded70aa48</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57fb0b293b6e45b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7d3f157d5d4e121</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eb49350fc0c3bff</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c2051a8e908817c</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff83660440c0810b</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5263c067a9d93c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0254aaa4115a0f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d6ce4a2306c3a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4128a682c7bf9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Integration Engineer II- AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b5b0a184e6ed2c87</t>
         </is>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=3612b0fc8bfb6ab5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Teachers Retirement System</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb97cb6b9e8a913</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Darkk Alpha Capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0162d13045a3367</t>
+          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,42 +1476,42 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer — RapidCanvas</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>David Joseph &amp; Company</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Databricks, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=99c7aecf044086c2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,42 +4616,42 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote - United States)</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, SQL Server, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,19 +4696,19 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a946d2db71d280</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Application Engineer IV</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer III, Platform Engineering</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Omnicell</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cranberry Township, PA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes, Git, CloudWatch</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0ef9b73a4ad4b77</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Application Engineer IV</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Carbo Ceramics, LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d10e8fe29e20e2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
+          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
+          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
+          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
+          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
+          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
+          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
+          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3df4cadd2708adf</t>
+          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,567 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e331a82a4ab0113</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0fa148b4d76cb12</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0941e3a211072d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82e649d860885dd8</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e8e06e7d196990</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=408d36db3edc62d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55d828aded70aa48</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57fb0b293b6e45b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d3f157d5d4e121</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb49350fc0c3bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2051a8e908817c</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff83660440c0810b</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5263c067a9d93c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0254aaa4115a0f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6ce4a2306c3a92</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4128a682c7bf9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5b0a184e6ed2c87</t>
+          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Software Engineer III - Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3267639dd0ee93d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Data Solutions Architect – Azure Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MINDBRIDGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
+          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DevIQ</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8293723295138e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Wayne, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
+          <t>https://www.indeed.com/viewjob?jk=3612b0fc8bfb6ab5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3612b0fc8bfb6ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Oracle HCM Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Lavisee Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=242b4333150528fa</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Darkk Alpha Capital</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, PostgreSQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f68d653a407d3790</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DATA Engineer with Healthcare background</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23db276cee90e934</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Software Engineer - Database</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>TP-LINK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Platform &amp; Backend Focus)</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e87a97e8641f456</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Engineer — RapidCanvas</t>
+          <t>Sr. Software Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>David Joseph &amp; Company</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Databricks, Scala, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c7aecf044086c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los</t>
+          <t>Application Support Analyst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Databricks, Scala, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=99c7aecf044086c2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Senior Data Platform Architect</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Troon</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,19 +4696,19 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Manufacturing Data Systems Engineer</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Application Engineer IV</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Manufacturing Data Systems Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Application Engineer IV</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer III (Platform)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer III (Platform)</t>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5053,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,497 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d2dba42ea7b46</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Sr. Programmer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5d8d0b561c6c008</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Sacramento, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d7e6a1de777704</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=930d2726ed50d1a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0066d0bcfffab778</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a84eebc46b7bb45a</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6166003e4d083c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=970c4df1d0044efd</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07fca26cae287b9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25f4db2419f6936e</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=373c81834c6c47aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f047826ac4929ff2</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Integration Engineer II- AI &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, ETL, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a77683d18934edc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist / Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Tergar International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c69d5a1a971e22e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BONbLOC</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Google Cloud Platform, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203332422aec13ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Applied Architect (.NET &amp; Databricks)</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3c1f686434a6c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tergar International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Hempstead, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Decision Foundry</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, SNS, API Gateway, IAM, RDS, Azure</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4373bea89867ea0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
+          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad46bda20740e85</t>
+          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hempstead, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f474c30f7d29a034</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e15a4878d8c2188</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bronx, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,137 +916,137 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68aba97affeb5808</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Integration Engineer – Credit Risk - SDIE 26-06669</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Synstack Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8305c2858081dfcf</t>
+          <t>https://www.indeed.com/viewjob?jk=6f22b99fcc46a1ed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wayne, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3612b0fc8bfb6ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oracle HCM Developer</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lavisee Technologies</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac70b1298ea5c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>eHub</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>Senior Data Engineer-Onsite</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242b4333150528fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,94 +1441,94 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Integration Technical Architect (AWS/AI)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6eff26eac5f1144c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Solutions Architect (Remote, US Only)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>Progspectra</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=55ed86a960ce796d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AWS Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer - Database</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Cloud Storage, Scala, Kafka, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4b22f5ed4795cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798275d9488660df</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AWS Data Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HDI Global Insurance Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094f4152c1c3b844</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,112 +3391,112 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer (Fintech)</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CADRE GOVERNMENT SOLUTIONS</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2939e578451e049f</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=b6f3b09a9c1f5b31</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Demand Works Media LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer II - QuantumBlack, AI by McKinsey</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, dbt, MLOps</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0333886fec2326</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff7d97185671a3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git, Python</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5b87ce57fff653</t>
+          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Dask, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da87067b7b52c98</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EY-Parthenon - Strategy and Execution - Growth Platforms - Data Scientist - Sr Associate/Consultant</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f1573e4d5b380e</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, dbt, Airflow</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde4359b0781ac36</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Engineer — RapidCanvas</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>David Joseph &amp; Company</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Kafka, MongoDB, Talend, Power BI</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a5e66ee1c26d4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,124 +4486,124 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
+          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>VetsEZ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Application Support Analyst</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Databricks, Scala, DynamoDB, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99c7aecf044086c2</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4612,11 +4612,11 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Platform Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Troon</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d00826f43274ea34</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Sr. Programmer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>COMMUNITY BEHAVIORAL HEALTH</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4695,461 +4695,6 @@
         </is>
       </c>
       <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Managed Services Engineer III</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Forward Deployed Data Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>CoorsTek</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Golden, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Application Engineer IV</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Fort Meade, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, Dataflow, Spark, PySpark, Scala, MongoDB</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9da97f7358a9449</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Manufacturing Data Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Ion Storage Systems</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Beltsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfacddbdda92507</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>In-N-Out Burger</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Engineer III (Platform)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>MAPFRE Insurance</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Webster, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Scala, Data Modeling, ETL, CI/CD, Jenkins, Jenkins, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c94972b0ddefdba</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>VetsEZ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Carbo Ceramics, LLC</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ELT</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d10e8fe29e20e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Sr. Programmer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
         </is>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,12 +818,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (.NET / Azure)</t>
+          <t>AI/ML Architect with Databricks , AWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
+          <t>https://www.indeed.com/viewjob?jk=830c3438f0d2663d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b304f9c143a865</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc95db0c4e95e26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Senior Data Engineer (.NET / Azure)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=e69f8437775af7c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Synstack Technologies</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, ECS, Azure, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,94 +951,94 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f22b99fcc46a1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eHub</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a462b164d07d7ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Onsite</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79f877445f165bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,52 +1186,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>Aureon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d34924c7fa34c06a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Integration Technical Architect (AWS/AI)</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eff26eac5f1144c</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Solutions Architect (Remote, US Only)</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Progspectra</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ed86a960ce796d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79ec357fcd98fdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Spark, PySpark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b09ade6f09c89eb1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Integration Technical Architect (AWS/AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
+          <t>https://www.indeed.com/viewjob?jk=6eff26eac5f1144c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Databricks Solutions Architect (Remote, US Only)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Progspectra</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
+          <t>https://www.indeed.com/viewjob?jk=55ed86a960ce796d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,147 +3391,147 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd033c06ef261546</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Tableau Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Tableau, MLOps, MLflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6f3b09a9c1f5b31</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, Snowflake, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea671c360a6a09f8</t>
+          <t>https://www.indeed.com/viewjob?jk=301853b8fccc1809</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>BI and AI Automation Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Demand Works Media LLC</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,104 +3846,104 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26540d1cf37e6176</t>
+          <t>https://www.indeed.com/viewjob?jk=9063c5940585caea</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Engineer — RapidCanvas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>David Joseph &amp; Company</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Java Developer (Connected Services)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>AI Engineer — RapidCanvas</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>David Joseph &amp; Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Product Engineer (Remote Opportunitty)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VetsEZ</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4a60afd289d560</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>Python Web Application Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>IntelliDyne</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
+          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9c11c9c5d79b69</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ac532ab4d53203</t>
+          <t>https://www.indeed.com/viewjob?jk=97504e4a10013b10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Programmer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>COMMUNITY BEHAVIORAL HEALTH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,1277 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93628dfc1ed2e57f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7083633f75338f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f0ad9dd289acaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adcfd80d8ddd1797</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bb4ff161f79eb97</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5831cc5d3ed71831</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fb1a59f2ca0aeb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac92f9aded586f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65400d21e4dfaa86</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=907d088ad4ce8817</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef81c336a7e79cf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61595787db57fa06</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf665a655bb76a60</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=226a2a348809de06</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=902f62fb402f51b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=390f0e5e656d9f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd0a54957f419fd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8487f3d26792e9c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d3775900918d6f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7bba88de037d9fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a22f7446a850802</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac6674e24dedb4bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73face8a34de6a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5621a1c72043ad69</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20019031158d9ceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a58fac0f49f9d30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4086f935d5f155c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8501f1696a12916f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fbc505460e5f197</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e72d71a6e24e91f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76d1a5cf74c11970</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78682532bd90175</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35b0d779964d6040</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff13af8a1356cc7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06ccd6e8311d5e0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd9d4ddad5f8751a</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=121a767a69ec77df</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Python Developer (Linux exp)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, PostgreSQL, MySQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdc98d9c47321a48</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-05.xlsx
+++ b/results/job_matches_2026-06-05.xlsx
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Expert / Data Lakehouse Consultant</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bilink Corp</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ef7670a3dacf51f</t>
+          <t>https://www.indeed.com/viewjob?jk=53ff12a0a5a571cd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Platform</t>
+          <t>Data Solutions Architect – Azure Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MINDBRIDGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2aebd4405215d87</t>
+          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Solutions Architect – Azure Databricks</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MINDBRIDGE SOLUTIONS INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e70c6ae374fe7d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b03d7c92e1f21c5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tergar International</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,52 +591,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7eec213f6c00cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5772ff395b2cde45</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7a7675d2646cd</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps, CI/CD</t>
+          <t>AWS, Redshift, IAM, Azure, GCP, BigQuery, Cloud Storage, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba9d8e9033d19ed9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Opiniion</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, Azure, Vertex AI, Spark, Scala, NoSQL, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4b877f69f2d40c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
+          <t>Full Stack Developer (Integrations &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d9ad5ad2072263</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Engineer – Java Spring Boot w/ Full Stack Option</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Department of City Planning</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,94 +1056,94 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
+          <t>https://www.indeed.com/viewjob?jk=dc2626116e7624e8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ReactJS with Azure developer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=646a3daa8dc34065</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7a82ae76adde3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Living Spaces</t>
+          <t>Department of City Planning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>La Mirada, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Spark, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=997ff73d3d72b982</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
+          <t>ReactJS with Azure developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Manscaped</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
+          <t>Azure, Blob Storage, Spark, PySpark, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb8dd8900af0c8a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
+          <t>Software Engineer II, Full Stack - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,77 +1221,77 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, BigQuery, Cloud Storage, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5b5d3254dd04f4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Living Spaces</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>La Mirada, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a573fb5cab0a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=174248a1c04ee5d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Senior Systems &amp; Platform Engineer, Enterprise Apps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Manscaped</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4090e7484beae777</t>
+          <t>https://www.indeed.com/viewjob?jk=78dc384749455c9e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer</t>
+          <t>Full Stack Developer (.NET &amp; Angular) – Azure Cloud</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5741e2b48538b3e9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer - Power BI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aureon</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34924c7fa34c06a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d20bf479b606085</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI/ML Engineer with Drone Imagery</t>
+          <t>Senior AWS Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,42 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eaba1f6b997fc8a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer with Drone Imagery</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Madagoni LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=21ff0351d35be0f9</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Madagoni LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3ec55ccf11bf4e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Integration Engineer (Senior Associate)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
+          <t>https://www.indeed.com/viewjob?jk=82f7476cf0abb572</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Platform Integration Engineer (Senior Associate)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
+          <t>https://www.indeed.com/viewjob?jk=21ffac673f9e5e45</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
+          <t>https://www.indeed.com/viewjob?jk=5d21417725ec301b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e053efd9a837ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb410896822ce80</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Solutions Architect (Remote, US Only)</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Progspectra</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ed86a960ce796d</t>
+          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Software Development Engineer – Imaging Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Radian Group Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
+          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7404c3655de04dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bcd1876902912f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9b38178b754383</t>
+          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82b6e9e211f61d4</t>
+          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a620a55e826a673d</t>
+          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902e213debac8809</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1016648c0f0d5d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc1d5f8003f7600</t>
+          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74fbd56cbb6e1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17103584ffb6e509</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cd476fc679a04a</t>
+          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb9b103396ef75e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1885c3e7464f9bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8189bb7df0daff</t>
+          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d53b87a5ed021b7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85395c75059dc994</t>
+          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b92f217fa630744</t>
+          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8564e7eebd81568f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c751ca8403940e46</t>
+          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec5266cd24c2dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265bf1290caccb77</t>
+          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d24914a82cfe666e</t>
+          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05705973a9378d80</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=795911acb1bee51f</t>
+          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0942fc02191a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=617495dbf623e38c</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52f3fc7ec6df2ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b93989e7d84</t>
+          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4581cdcaed5f9f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c766afcec299ad51</t>
+          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77cb2c150ee12d87</t>
+          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d75093b6fcd02c5</t>
+          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676f9ebac1172832</t>
+          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454de9f58fa31614</t>
+          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba87ffa60d4ea16b</t>
+          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954bc66fa74e678c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3adae39628854eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a7a440e90ffe87a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd03d55c286c7fd</t>
+          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5e7399fcd292254</t>
+          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693602db725cd736</t>
+          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059b9c50895f7fee</t>
+          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e189e5672a8c8a33</t>
+          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9c5376661bd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adba19e5f6f34e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0494adf7cd3b47d6</t>
+          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6a0794cdf7814e0</t>
+          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd03a4989d1f2d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer – Imaging Platform</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Radian Group Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Google Cloud Platform, GCP, Cloud Storage, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, RDS, Snowflake, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77011faf16332680</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a20fd70866cf85</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22d9b89413d8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tableau Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>TG Administration LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7f11b8f38a8ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=e9e73f395d9ef664</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Azure Engineer (Associate)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59f3b1d389f972e</t>
+          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Azure Engineer (Associate)</t>
+          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e98785342dc04b</t>
+          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Newburgh, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385dd5972eb6dd82</t>
+          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Newburgh, NY, US USA</t>
+          <t>New Rochelle, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a61e6df431f6147</t>
+          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New Rochelle, NY, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f2149793d5db9d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Yonkers, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8767e19975ee4ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Credit Risk Data Engineer - New York, NY - RDE26-06669</t>
+          <t>SDET AI Architect role</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14789b3132768e61</t>
+          <t>https://www.indeed.com/viewjob?jk=c169be2658178cd6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Development Engineer In Test, ML/AI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, Snowflake, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301853b8fccc1809</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer In Test, ML/AI</t>
+          <t>Associate - Full Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,69 +3881,69 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b49d9429473d67</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate - Full Stack Developer</t>
+          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9923838d6f3cba</t>
+          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Digital Banking &amp; Payments</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sunward</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Kafka, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bbcfafb38b8635</t>
+          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Cayuse Holdings</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5b8ffd36870fad</t>
+          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sunward</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,29 +4021,29 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d80ccc2355815fc</t>
+          <t>https://www.indeed.com/viewjob?jk=82fe8f468cf74df4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Full Stack Web Development – GCP &amp; Vertex AI Focus</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, ETL, ELT, Tableau, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f660da5ba96d068e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecb968fef1744db</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
+          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Analyst — AI-Driven Insights</t>
+          <t>Senior Software Engineer, Scientific System of Record</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>David's Bridal</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e573f908d6ce2f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angeles</t>
+          <t>URBN Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>URBN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48345cae6728d8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Scientific System of Record</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, dbt, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,129 +4206,129 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e75312efc2a4179</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef62050b69ea736</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>URBN Senior DevOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>URBN</t>
+          <t>Qnity</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535d8204a8558bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f794016856a71562</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Java Developer (Connected Services)</t>
+          <t>Data Engineer Associate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b01571494179411</t>
+          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Engineer — RapidCanvas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>David Joseph &amp; Company</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Dask, NoSQL, MLOps, MLflow, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82825a4b70114e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b5783dbfc8eb97f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer Associate</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Roseville, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Scala, Oracle, NoSQL, ETL, ELT, MLOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64684543a43aac31</t>
+          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ed2769c487c743</t>
+          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Managed Services Engineer III</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1623a93394ec68b8</t>
+          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Managed Services Engineer III</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d223961163a5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>In-N-Out Burger</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbe256f9b09a7e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Site Reliability Engineer I- Operations</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>In-N-Out Burger</t>
+          <t>Utah Valley University</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Orem, UT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Spark, Scala, Oracle, Dimensional Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8e13676bc61f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Python Web Application Developer</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>IntelliDyne</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=085b37bc2f384dd8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>People Analytics AI Engineer</t>
+          <t>Python Web Application Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>IntelliDyne</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
+          <t>https://www.indeed.com/viewjob?jk=68462d5c7447b1bc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I- Operations</t>
+          <t>People Analytics AI Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Utah Valley University</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Orem, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,24 +4616,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, MySQL, Splunk, CI/CD, CloudWatch, Azure Monitor, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafdc7b6e7a9e469</t>
+          <t>https://www.indeed.com/viewjob?jk=5b3fd2f9a605cf45</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Scientist Associate - Product, Experience and Technology (PXT) Analytics Team</t>
+          <t>Data Scientist - Sr. Associate - Product, Experience and Technology (PXT) Analytics Team</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
